--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45904</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>45372</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>44907</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>46002</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         <v>45869</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>46008</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>46029</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>46177</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>46132</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45870</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44494</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>45996</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>44693</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>45170</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>45092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>44740</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45429</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3932,7 +3932,7 @@
         <v>44593</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4147,7 +4147,7 @@
         <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
         <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45106</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4462,7 +4462,7 @@
         <v>45369</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         <v>46021</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         <v>46197</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45614</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>45246</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5120,7 +5120,7 @@
         <v>45117</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5230,7 +5230,7 @@
         <v>44580</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         <v>45869</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         <v>45705</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5555,7 +5555,7 @@
         <v>44873</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
         <v>44507</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>44886</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
         <v>44841</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>44673</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5925,7 +5925,7 @@
         <v>44711</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44481</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>44523</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44866</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44834</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44665</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44832</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44747</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>44673</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44852</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44832</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6836,7 +6836,7 @@
         <v>44832</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         <v>44537</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44461</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7060,7 +7060,7 @@
         <v>44545</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>44538</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7206,7 +7206,7 @@
         <v>44481</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>44728</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>44523</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44460</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>44545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45591</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45460</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44711</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8404,7 +8404,7 @@
         <v>45758</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8482,7 +8482,7 @@
         <v>44557</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>44657</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>44728</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45204</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>44545</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8852,7 +8852,7 @@
         <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8930,7 +8930,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>45163</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45327</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45670</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45729</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45335</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         <v>45190</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>45020</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9841,7 +9841,7 @@
         <v>45141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         <v>45086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9987,7 +9987,7 @@
         <v>45062</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>45720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45146</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44887</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10435,7 +10435,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>45733</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>45467</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10732,7 +10732,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10810,7 +10810,7 @@
         <v>44836</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44809</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11034,7 +11034,7 @@
         <v>45554</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11107,7 +11107,7 @@
         <v>45943</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         <v>45156</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>45678</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>45050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>45511</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>45670</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
         <v>45782</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11628,7 +11628,7 @@
         <v>45896</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11701,7 +11701,7 @@
         <v>45896</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11774,7 +11774,7 @@
         <v>45614</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11852,7 +11852,7 @@
         <v>45902</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11930,7 +11930,7 @@
         <v>45911</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12003,7 +12003,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12081,7 +12081,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12159,7 +12159,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12315,7 +12315,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>45918</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12461,7 +12461,7 @@
         <v>45187</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12534,7 +12534,7 @@
         <v>44692</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>45924</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>44914</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12753,7 +12753,7 @@
         <v>45259</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>44803</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>45929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12972,7 +12972,7 @@
         <v>45924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>45930</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         <v>45320</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13201,7 +13201,7 @@
         <v>44937</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13274,7 +13274,7 @@
         <v>45713</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13352,7 +13352,7 @@
         <v>46146</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>45943</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13503,7 +13503,7 @@
         <v>45943</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>45943</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>45943</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13737,7 +13737,7 @@
         <v>45945</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>44557</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13883,7 +13883,7 @@
         <v>45758</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13961,7 +13961,7 @@
         <v>45947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44980</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14112,7 +14112,7 @@
         <v>45021</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14185,7 +14185,7 @@
         <v>45152</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14258,7 +14258,7 @@
         <v>45462</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>44979</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14409,7 +14409,7 @@
         <v>45954</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>45954</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>46152</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>45390</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14716,7 +14716,7 @@
         <v>45880</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>45877</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14872,7 +14872,7 @@
         <v>45877</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45965</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45965</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45965</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45965</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>44886</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45027</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>45587</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45020</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>44488</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45337</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45537</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15768,7 +15768,7 @@
         <v>45020</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44497</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>45981</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45559</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16065,7 +16065,7 @@
         <v>45079</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16138,7 +16138,7 @@
         <v>45324</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>45551</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>45986</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45989</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45817</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>46085</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45145</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45614</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16903,7 +16903,7 @@
         <v>45995</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>45996</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>46167</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45747</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17215,7 +17215,7 @@
         <v>45809</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17288,7 +17288,7 @@
         <v>46003</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17361,7 +17361,7 @@
         <v>46003</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>45013</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17507,7 +17507,7 @@
         <v>45552</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17585,7 +17585,7 @@
         <v>46008</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>46008</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>44980</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17814,7 +17814,7 @@
         <v>44908</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45747</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17970,7 +17970,7 @@
         <v>45072</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18043,7 +18043,7 @@
         <v>45020</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45429</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18189,7 +18189,7 @@
         <v>45086</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18262,7 +18262,7 @@
         <v>46030</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>44872</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>44886</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18491,7 +18491,7 @@
         <v>44886</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18564,7 +18564,7 @@
         <v>44887</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45769</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>46036</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>44515</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>45629</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>46044</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19017,7 +19017,7 @@
         <v>45580</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19090,7 +19090,7 @@
         <v>45600</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
         <v>45600</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19246,7 +19246,7 @@
         <v>45222</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19324,7 +19324,7 @@
         <v>45462</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19402,7 +19402,7 @@
         <v>46069</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45117</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45078</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>46071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>44858</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19782,7 +19782,7 @@
         <v>44650</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19855,7 +19855,7 @@
         <v>46080</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>44831</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>46189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45973</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45917</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>46196</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20318,7 +20318,7 @@
         <v>45226</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>46101</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45614</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45020</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>46244</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20771,7 +20771,7 @@
         <v>46199</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20844,7 +20844,7 @@
         <v>45156</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45673</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20995,7 +20995,7 @@
         <v>44822</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21068,7 +21068,7 @@
         <v>45702</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21141,7 +21141,7 @@
         <v>45222</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21214,7 +21214,7 @@
         <v>45301</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21287,7 +21287,7 @@
         <v>45343</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>45020</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44859</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21516,7 +21516,7 @@
         <v>45581</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21589,7 +21589,7 @@
         <v>45937</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
         <v>45747</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>46247</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>45364</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>46244</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>46247</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22042,7 +22042,7 @@
         <v>45146</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22115,7 +22115,7 @@
         <v>46251</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22193,7 +22193,7 @@
         <v>45062</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22266,7 +22266,7 @@
         <v>44904</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>46205</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22412,7 +22412,7 @@
         <v>46205</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22485,7 +22485,7 @@
         <v>46205</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22558,7 +22558,7 @@
         <v>46205</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22631,7 +22631,7 @@
         <v>44858</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22709,7 +22709,7 @@
         <v>45258</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22787,7 +22787,7 @@
         <v>44914</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22865,7 +22865,7 @@
         <v>45758</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22943,7 +22943,7 @@
         <v>45301</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23016,7 +23016,7 @@
         <v>45301</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23089,7 +23089,7 @@
         <v>45163</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>44672</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>45072</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23313,7 +23313,7 @@
         <v>46248</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23391,7 +23391,7 @@
         <v>46218</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
         <v>46265</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23537,7 +23537,7 @@
         <v>45365</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23610,7 +23610,7 @@
         <v>45210</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23683,7 +23683,7 @@
         <v>44942</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23756,7 +23756,7 @@
         <v>45089</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>46178</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23907,7 +23907,7 @@
         <v>45986</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45020</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>45020</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>45301</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24204,7 +24204,7 @@
         <v>46226</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24277,7 +24277,7 @@
         <v>46226</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>46273</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24428,7 +24428,7 @@
         <v>45554</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45782</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24574,7 +24574,7 @@
         <v>46274</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>46275</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24725,7 +24725,7 @@
         <v>46274</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45342</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>46276</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>46276</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45147</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>46238</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25168,7 +25168,7 @@
         <v>46238</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45797</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25319,7 +25319,7 @@
         <v>45797</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25392,7 +25392,7 @@
         <v>46218</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25465,7 +25465,7 @@
         <v>46239</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25543,7 +25543,7 @@
         <v>46188</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25621,7 +25621,7 @@
         <v>45467</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25694,7 +25694,7 @@
         <v>46239</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25772,7 +25772,7 @@
         <v>45809</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>45222</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25918,7 +25918,7 @@
         <v>45825</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25996,7 +25996,7 @@
         <v>45855</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>45860</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26142,7 +26142,7 @@
         <v>45867</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26220,7 +26220,7 @@
         <v>45867</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>45867</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26376,7 +26376,7 @@
         <v>45869</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26454,7 +26454,7 @@
         <v>45860</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26527,7 +26527,7 @@
         <v>45860</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45860</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26673,7 +26673,7 @@
         <v>45537</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45929</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26824,7 +26824,7 @@
         <v>45943</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45996</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45996</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46189</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>46189</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>46196</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46002</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46029</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46132</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46177</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45870</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>46101</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>45092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45170</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45369</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44580</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45869</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>46197</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>46286</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45610</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44873</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44507</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44711</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44866</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44834</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44665</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44832</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44747</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44832</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44537</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44545</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44538</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44481</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44488</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45729</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45429</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45554</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45301</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45467</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45021</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>46030</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44858</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>46036</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45902</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45670</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45911</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44692</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45551</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45559</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45924</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45222</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>46071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44886</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44886</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45552</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45930</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>46080</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45809</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45614</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45943</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45943</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44872</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>46101</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44672</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44942</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45954</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45954</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45629</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45670</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45877</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45877</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45880</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45020</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45020</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45965</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44497</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45145</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45462</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45981</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45163</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44809</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45581</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45989</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45989</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45996</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45072</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45782</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45020</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46003</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>46008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45301</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44858</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45072</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45062</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45086</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>46146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>44886</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45117</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45222</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>46152</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45337</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44836</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46085</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44904</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45050</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45809</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45078</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44557</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45825</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>44515</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45020</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45747</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>44980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44914</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45867</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45867</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45869</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45156</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45020</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45020</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46189</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45152</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45591</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45146</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45604</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45860</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45190</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>46205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>44657</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45769</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45141</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44822</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45698</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>46218</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44650</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45187</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45222</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45720</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>46265</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>46178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45320</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45327</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>46226</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45758</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>46274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45364</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44831</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>46273</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>46276</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46276</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45733</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>46275</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45462</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45702</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46239</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>44979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46286</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46274</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45062</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>46244</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45020</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44914</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45924</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>46290</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45301</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45301</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45600</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45600</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44614</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45324</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45210</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45226</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45365</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45390</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45747</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45511</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44545</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44859</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45758</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45335</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45301</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45147</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45342</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45943</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>46196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46002</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46029</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46132</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46177</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45870</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46044</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>46101</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>45092</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>44740</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>45170</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45117</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>46021</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>45369</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>45190</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4697,7 +4697,7 @@
         <v>44593</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         <v>44580</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4912,7 +4912,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45869</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>46197</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>46286</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45246</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45610</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>44873</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5859,7 +5859,7 @@
         <v>44507</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5932,7 +5932,7 @@
         <v>44886</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         <v>44841</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>44711</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6229,7 +6229,7 @@
         <v>44473</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>44481</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44866</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44834</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44665</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>44832</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44747</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>44673</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>44852</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         <v>44832</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7062,7 +7062,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>44537</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7213,7 +7213,7 @@
         <v>44545</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>44538</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7359,7 +7359,7 @@
         <v>44481</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7661,7 +7661,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7817,7 +7817,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7890,7 +7890,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8041,7 +8041,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8114,7 +8114,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44488</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>45747</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8411,7 +8411,7 @@
         <v>45729</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45429</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45554</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8635,7 +8635,7 @@
         <v>45301</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         <v>45222</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         <v>45467</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>45259</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45258</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>45021</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9078,7 +9078,7 @@
         <v>46030</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>45797</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9229,7 +9229,7 @@
         <v>44858</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>46036</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>45896</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9453,7 +9453,7 @@
         <v>45896</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         <v>46044</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9599,7 +9599,7 @@
         <v>45902</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44908</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9755,7 +9755,7 @@
         <v>45467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>45670</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>45911</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>44692</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10052,7 +10052,7 @@
         <v>45918</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10125,7 +10125,7 @@
         <v>45917</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
         <v>45551</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45917</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10359,7 +10359,7 @@
         <v>45917</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10437,7 +10437,7 @@
         <v>45917</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45559</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44937</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45919</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>46069</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45924</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10890,7 +10890,7 @@
         <v>45222</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>46071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         <v>44886</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         <v>44886</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11182,7 +11182,7 @@
         <v>44887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11260,7 +11260,7 @@
         <v>45552</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11338,7 +11338,7 @@
         <v>45929</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11411,7 +11411,7 @@
         <v>45930</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>46080</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45809</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>45580</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45614</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11869,7 +11869,7 @@
         <v>44711</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11947,7 +11947,7 @@
         <v>45973</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45943</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>45943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12259,7 +12259,7 @@
         <v>45943</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12337,7 +12337,7 @@
         <v>44872</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>45945</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>46101</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45947</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44672</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>44942</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>45954</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12868,7 +12868,7 @@
         <v>45954</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>45629</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13024,7 +13024,7 @@
         <v>45670</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>45877</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45877</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13253,7 +13253,7 @@
         <v>45880</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>45089</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45020</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45020</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45965</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         <v>45965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13842,7 +13842,7 @@
         <v>44497</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>45145</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>45462</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14066,7 +14066,7 @@
         <v>45981</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14139,7 +14139,7 @@
         <v>45343</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14217,7 +14217,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14373,7 +14373,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>45937</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>45163</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14602,7 +14602,7 @@
         <v>44809</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14675,7 +14675,7 @@
         <v>45581</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14748,7 +14748,7 @@
         <v>45989</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45989</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>45995</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45996</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>45072</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>45027</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15284,7 +15284,7 @@
         <v>45163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>45782</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>45020</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>46003</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46003</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15654,7 +15654,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>46008</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
         <v>45678</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15966,7 +15966,7 @@
         <v>45301</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45673</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>44858</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45072</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45062</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16341,7 +16341,7 @@
         <v>45086</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>46146</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>44886</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>45117</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45222</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>46152</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45747</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>44887</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16940,7 +16940,7 @@
         <v>45337</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>44836</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>45817</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>46085</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17232,7 +17232,7 @@
         <v>44904</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17305,7 +17305,7 @@
         <v>45050</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45809</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45078</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>44557</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17602,7 +17602,7 @@
         <v>44557</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17675,7 +17675,7 @@
         <v>45825</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45086</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>46167</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>44515</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>45020</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45614</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45747</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18206,7 +18206,7 @@
         <v>45758</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>45855</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45860</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>44980</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
         <v>44914</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>45146</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>45867</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45867</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45867</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45537</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45869</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45156</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45713</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45020</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19346,7 +19346,7 @@
         <v>45020</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19419,7 +19419,7 @@
         <v>45020</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19492,7 +19492,7 @@
         <v>46189</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19570,7 +19570,7 @@
         <v>45152</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45591</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45146</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>45604</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19862,7 +19862,7 @@
         <v>45917</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19935,7 +19935,7 @@
         <v>45860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>46196</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>45860</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20232,7 +20232,7 @@
         <v>45860</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>46199</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>45190</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>44803</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>46205</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
         <v>46205</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20675,7 +20675,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         <v>46205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>46251</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>44657</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>45769</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21050,7 +21050,7 @@
         <v>45141</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>44822</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45698</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45156</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>44728</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45986</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>46218</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>44650</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21722,7 +21722,7 @@
         <v>45187</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21795,7 +21795,7 @@
         <v>45062</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45222</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21946,7 +21946,7 @@
         <v>45720</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22019,7 +22019,7 @@
         <v>46265</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>46178</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22170,7 +22170,7 @@
         <v>46226</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22243,7 +22243,7 @@
         <v>45320</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>45327</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>46226</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45758</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>46274</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22623,7 +22623,7 @@
         <v>45364</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22696,7 +22696,7 @@
         <v>44831</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>46273</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22852,7 +22852,7 @@
         <v>46274</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>46276</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>46276</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>45733</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23149,7 +23149,7 @@
         <v>46275</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>46238</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>45462</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23378,7 +23378,7 @@
         <v>45702</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>46238</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>46239</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>46239</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>46188</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>44979</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>46286</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23914,7 +23914,7 @@
         <v>46274</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>46218</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>46286</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24211,7 +24211,7 @@
         <v>45079</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24284,7 +24284,7 @@
         <v>45062</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>46287</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45301</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>46290</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24654,7 +24654,7 @@
         <v>45204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24727,7 +24727,7 @@
         <v>46244</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45020</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>44914</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24946,7 +24946,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25024,7 +25024,7 @@
         <v>45924</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>46290</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>46248</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25248,7 +25248,7 @@
         <v>45301</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25321,7 +25321,7 @@
         <v>45301</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25394,7 +25394,7 @@
         <v>45600</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25472,7 +25472,7 @@
         <v>45600</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25550,7 +25550,7 @@
         <v>44614</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45324</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25706,7 +25706,7 @@
         <v>45210</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45226</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45365</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>45390</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26003,7 +26003,7 @@
         <v>45747</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26081,7 +26081,7 @@
         <v>45511</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26154,7 +26154,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26232,7 +26232,7 @@
         <v>45259</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26383,7 +26383,7 @@
         <v>44545</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>44859</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26534,7 +26534,7 @@
         <v>45758</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26612,7 +26612,7 @@
         <v>45013</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26685,7 +26685,7 @@
         <v>45335</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>45301</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26836,7 +26836,7 @@
         <v>45554</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26909,7 +26909,7 @@
         <v>45782</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45147</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27055,7 +27055,7 @@
         <v>45342</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27128,7 +27128,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27206,7 +27206,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45943</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27357,7 +27357,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27435,7 +27435,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>46189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27669,7 +27669,7 @@
         <v>46196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46132</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45870</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>45170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45092</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44740</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44593</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44580</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45869</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>46197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>46286</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46296</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44873</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44507</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44711</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44832</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44866</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44711</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45591</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45758</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45460</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44545</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45204</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>46003</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45747</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>46008</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45301</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45301</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45062</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45163</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45327</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44614</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45729</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45335</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46044</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45797</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45222</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45919</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45918</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45190</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>46069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45141</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>46071</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45943</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45020</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45809</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45947</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>46080</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>45062</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45086</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45720</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45954</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45259</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45880</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45877</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45877</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45965</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45965</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45604</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45973</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45467</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46101</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45733</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45981</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>44836</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45995</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45554</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45678</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45050</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45511</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45301</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45343</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45581</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45614</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44809</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44692</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45782</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44914</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44803</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45860</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45867</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45867</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45867</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45869</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44557</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45152</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45462</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46146</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45390</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>46152</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44886</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45587</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45817</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45020</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44488</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>46085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45337</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45020</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>44497</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46167</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45559</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45079</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45324</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45860</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45860</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45747</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45860</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45145</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45614</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45747</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46189</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45013</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45552</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44980</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44908</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45020</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45429</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44872</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>44886</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44886</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44887</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45769</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46205</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44515</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45580</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>46218</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>46265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45600</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45600</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45222</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46178</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45986</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45462</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45117</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45078</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>46226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>46226</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46273</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44858</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44650</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>46274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46275</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46276</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46276</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>46239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46188</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45226</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46287</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46218</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46286</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46244</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45614</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>46274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45020</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45097</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45156</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45673</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>44822</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46290</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>46248</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>46247</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45702</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45222</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45020</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44859</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45747</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45364</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45062</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44904</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44858</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44914</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45758</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45301</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45301</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44672</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45365</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45210</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45089</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45020</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45020</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45301</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45554</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45782</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45342</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45147</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45943</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>46196</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>46002</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46132</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45870</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46002</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
         <v>45170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>46044</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46101</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>45092</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>44740</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>46021</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45911</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45117</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4373,7 +4373,7 @@
         <v>44593</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>44673</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4588,7 +4588,7 @@
         <v>44580</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         <v>45869</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>45610</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4908,7 +4908,7 @@
         <v>45106</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5013,7 +5013,7 @@
         <v>45369</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>46197</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>46286</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>45246</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>45705</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46296</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>44873</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>44507</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         <v>44886</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>44673</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6188,7 +6188,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6261,7 +6261,7 @@
         <v>44711</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         <v>44473</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6412,7 +6412,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6490,7 +6490,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7021,7 +7021,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7094,7 +7094,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7172,7 +7172,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7625,7 +7625,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>44523</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44832</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         <v>44803</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>44846</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44866</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8151,7 +8151,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8297,7 +8297,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>44711</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         <v>45591</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>45758</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44728</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>45460</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44657</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44545</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
         <v>45204</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9042,7 +9042,7 @@
         <v>46003</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         <v>45747</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>46003</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>46008</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>46008</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         <v>45301</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45301</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45062</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
         <v>45163</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45327</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45670</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45896</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10021,7 +10021,7 @@
         <v>46030</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10099,7 +10099,7 @@
         <v>44614</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10250,7 +10250,7 @@
         <v>45902</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10328,7 +10328,7 @@
         <v>45729</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>45335</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>45911</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10557,7 +10557,7 @@
         <v>46044</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45797</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10781,7 +10781,7 @@
         <v>45917</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10859,7 +10859,7 @@
         <v>45467</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10932,7 +10932,7 @@
         <v>45917</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45917</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45222</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45919</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45918</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>44887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>45924</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45929</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45930</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45190</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11687,7 +11687,7 @@
         <v>46069</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45141</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>46071</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45943</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45943</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45020</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45943</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
         <v>45943</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
         <v>45945</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45809</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>45947</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>46080</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>45062</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45086</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45720</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45954</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45146</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>45954</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45259</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45698</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45880</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45877</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45877</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45965</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13504,7 +13504,7 @@
         <v>45965</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13577,7 +13577,7 @@
         <v>45965</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45604</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45965</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45078</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>45973</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13952,7 +13952,7 @@
         <v>45467</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14025,7 +14025,7 @@
         <v>46101</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14103,7 +14103,7 @@
         <v>45733</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14176,7 +14176,7 @@
         <v>45981</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>45163</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14327,7 +14327,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14405,7 +14405,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>44836</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45989</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>45989</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45995</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>45996</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45554</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45222</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45156</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45678</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         <v>45050</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15238,7 +15238,7 @@
         <v>45511</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15311,7 +15311,7 @@
         <v>45670</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15384,7 +15384,7 @@
         <v>45301</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15457,7 +15457,7 @@
         <v>45343</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>45581</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>45614</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44809</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>45163</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45825</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16066,7 +16066,7 @@
         <v>45855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45187</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44692</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>45782</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16358,7 +16358,7 @@
         <v>44914</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16431,7 +16431,7 @@
         <v>45259</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16504,7 +16504,7 @@
         <v>44803</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45860</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16650,7 +16650,7 @@
         <v>45320</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>45867</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>45867</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16957,7 +16957,7 @@
         <v>45713</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45867</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>45869</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>44557</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45758</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>44980</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45152</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45462</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>44979</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46146</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45390</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>46152</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44886</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45027</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45587</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45817</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45020</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18311,7 +18311,7 @@
         <v>44488</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>46085</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18457,7 +18457,7 @@
         <v>45337</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18530,7 +18530,7 @@
         <v>45537</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45020</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18681,7 +18681,7 @@
         <v>44497</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>46167</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>45809</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>45559</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>45079</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45324</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45551</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>45860</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
         <v>45860</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45747</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
         <v>45860</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19509,7 +19509,7 @@
         <v>45145</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45614</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45747</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>46189</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19816,7 +19816,7 @@
         <v>45013</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19889,7 +19889,7 @@
         <v>45552</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45917</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>46196</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>44980</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20191,7 +20191,7 @@
         <v>44908</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20269,7 +20269,7 @@
         <v>45072</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45020</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>45429</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45086</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>46199</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20634,7 +20634,7 @@
         <v>44872</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>44886</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44886</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44887</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>45769</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46205</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46205</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>44515</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46205</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46205</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45580</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>46218</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21603,7 +21603,7 @@
         <v>46265</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21676,7 +21676,7 @@
         <v>45600</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45600</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>45222</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46178</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>45986</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22066,7 +22066,7 @@
         <v>45462</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22144,7 +22144,7 @@
         <v>45117</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45078</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>46226</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>46226</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22441,7 +22441,7 @@
         <v>46273</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>44858</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>44650</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>46274</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46275</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22821,7 +22821,7 @@
         <v>46274</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22894,7 +22894,7 @@
         <v>46276</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22967,7 +22967,7 @@
         <v>46276</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46238</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>44831</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23196,7 +23196,7 @@
         <v>46238</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23274,7 +23274,7 @@
         <v>46239</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>46188</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>46239</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45226</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>46287</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>46218</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>46286</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>46286</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23883,7 +23883,7 @@
         <v>46244</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23956,7 +23956,7 @@
         <v>45614</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>46274</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45020</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45097</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24331,7 +24331,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>45924</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45156</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>46247</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24628,7 +24628,7 @@
         <v>45673</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24706,7 +24706,7 @@
         <v>44822</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24779,7 +24779,7 @@
         <v>46290</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24852,7 +24852,7 @@
         <v>46248</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>46247</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45702</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45222</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45020</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>44859</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25305,7 +25305,7 @@
         <v>46251</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45747</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45364</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>45146</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45062</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>44904</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44858</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45258</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>44914</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45758</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26065,7 +26065,7 @@
         <v>45301</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26138,7 +26138,7 @@
         <v>45301</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45163</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>44672</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45072</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>45365</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>45210</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>44942</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>45089</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45020</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26800,7 +26800,7 @@
         <v>45020</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26873,7 +26873,7 @@
         <v>45301</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26946,7 +26946,7 @@
         <v>45554</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27019,7 +27019,7 @@
         <v>45782</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27092,7 +27092,7 @@
         <v>45342</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27165,7 +27165,7 @@
         <v>45147</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27238,7 +27238,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45943</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27467,7 +27467,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27545,7 +27545,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27623,7 +27623,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27701,7 +27701,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27779,7 +27779,7 @@
         <v>46196</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44907</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>45870</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46132</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44740</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45106</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45869</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46286</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>46296</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44886</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44832</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44803</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44846</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>44538</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>44832</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45117</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44545</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45747</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45429</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44887</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45337</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44836</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45747</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44488</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45554</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45050</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45222</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45078</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45226</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45390</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45020</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45259</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45747</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45258</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45511</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45587</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45021</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45259</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44545</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44914</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44858</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45301</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45554</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45156</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45020</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45020</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45782</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45670</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44692</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45342</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45591</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45551</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45559</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45146</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45924</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45222</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44886</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44887</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45552</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45930</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45614</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45797</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44711</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44657</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45809</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45943</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45629</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45670</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45141</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45947</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44822</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45020</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45698</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45156</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44728</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45954</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45954</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45877</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45877</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>44497</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45145</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44650</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45462</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45965</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45187</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45965</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45222</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45720</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45163</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45320</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45860</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45327</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45027</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45867</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45869</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45758</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45020</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45364</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>44831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45860</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45733</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46101</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45673</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44858</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45462</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45986</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45702</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45086</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45989</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44979</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>44886</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45996</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45079</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46003</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46003</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45301</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45343</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46008</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45204</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44809</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45581</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45020</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45301</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45782</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45600</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45943</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>46044</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45301</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46069</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46152</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46080</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45809</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>46167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45747</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45917</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46196</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46199</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46205</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46205</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46205</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45986</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46265</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46178</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46226</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46226</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46273</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46274</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46276</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46276</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46275</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46239</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>46286</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>46274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46218</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>46286</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46244</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>46287</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>46247</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>46290</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45924</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46290</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>46248</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46251</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>46300</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>46300</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45537</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45929</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45943</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45996</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46189</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46196</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44907</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>45532</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>45870</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2375,7 +2375,7 @@
         <v>46132</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>46029</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>46008</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46177</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45092</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>45429</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>44740</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>46002</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>46044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>45106</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45610</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45911</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45117</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4583,7 +4583,7 @@
         <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>44580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>45869</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5117,7 +5117,7 @@
         <v>45190</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>46021</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         <v>45246</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46197</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5561,7 +5561,7 @@
         <v>46286</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>46303</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45705</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>46296</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44873</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44507</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44886</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44841</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44673</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44711</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>44481</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6985,7 +6985,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         <v>44832</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7214,7 +7214,7 @@
         <v>44852</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         <v>44803</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44481</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7584,7 +7584,7 @@
         <v>44728</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7662,7 +7662,7 @@
         <v>44846</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         <v>44866</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7813,7 +7813,7 @@
         <v>44575</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         <v>44747</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7964,7 +7964,7 @@
         <v>44538</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         <v>44523</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8110,7 +8110,7 @@
         <v>44832</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         <v>44523</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>45117</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         <v>44545</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8485,7 +8485,7 @@
         <v>45747</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45429</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
         <v>44887</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>45337</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44836</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>45747</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44488</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45554</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>45210</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45050</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45301</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45222</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45078</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>44557</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44557</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9824,7 +9824,7 @@
         <v>45467</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9897,7 +9897,7 @@
         <v>45226</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>45365</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>45390</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>44515</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45020</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>45614</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10345,7 +10345,7 @@
         <v>45758</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>45259</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>45747</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>45258</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10652,7 +10652,7 @@
         <v>45511</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10803,7 +10803,7 @@
         <v>44980</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>45587</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>45021</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>45259</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11100,7 +11100,7 @@
         <v>45097</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11178,7 +11178,7 @@
         <v>44545</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44859</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11329,7 +11329,7 @@
         <v>44914</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11407,7 +11407,7 @@
         <v>45758</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>45146</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11631,7 +11631,7 @@
         <v>45896</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44858</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11782,7 +11782,7 @@
         <v>45902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>45013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>45335</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45301</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45537</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>45554</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44908</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45156</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45713</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45911</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45020</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45020</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>45020</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>45782</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>45147</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>45670</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12980,7 +12980,7 @@
         <v>45918</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>45917</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44692</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13204,7 +13204,7 @@
         <v>45342</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13277,7 +13277,7 @@
         <v>45917</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>45917</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>45917</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>45152</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>45591</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>45919</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13730,7 +13730,7 @@
         <v>45551</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45559</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>44937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45146</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45924</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45222</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>44886</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44886</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44887</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45552</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>45078</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45930</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14777,7 +14777,7 @@
         <v>45580</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14850,7 +14850,7 @@
         <v>45614</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45614</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45797</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45190</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>44711</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>45467</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>44803</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15381,7 +15381,7 @@
         <v>44872</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>44657</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15532,7 +15532,7 @@
         <v>45769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15610,7 +15610,7 @@
         <v>45809</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15683,7 +15683,7 @@
         <v>44672</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15756,7 +15756,7 @@
         <v>45943</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15834,7 +15834,7 @@
         <v>45943</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15912,7 +15912,7 @@
         <v>45943</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>45943</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16068,7 +16068,7 @@
         <v>45945</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>44942</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16214,7 +16214,7 @@
         <v>45629</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         <v>45670</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16365,7 +16365,7 @@
         <v>45141</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16438,7 +16438,7 @@
         <v>45947</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16516,7 +16516,7 @@
         <v>44822</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16589,7 +16589,7 @@
         <v>45089</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>45020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16735,7 +16735,7 @@
         <v>45020</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>45698</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>45156</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         <v>44728</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45954</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17188,7 +17188,7 @@
         <v>45954</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45877</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17344,7 +17344,7 @@
         <v>45877</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
         <v>44497</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17495,7 +17495,7 @@
         <v>45880</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17573,7 +17573,7 @@
         <v>45145</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17646,7 +17646,7 @@
         <v>44650</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17719,7 +17719,7 @@
         <v>45462</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45460</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45965</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45187</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>45965</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45062</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>45965</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45222</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45163</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>45720</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18464,7 +18464,7 @@
         <v>45163</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18542,7 +18542,7 @@
         <v>45825</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18620,7 +18620,7 @@
         <v>44980</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>45072</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45855</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18839,7 +18839,7 @@
         <v>45320</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45860</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45327</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19068,7 +19068,7 @@
         <v>45027</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19146,7 +19146,7 @@
         <v>45867</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45867</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>45869</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45758</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45020</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45364</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>44831</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45678</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45860</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>45981</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45860</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45860</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45733</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46101</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>45673</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>44858</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45462</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>45986</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45986</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20671,7 +20671,7 @@
         <v>45702</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20744,7 +20744,7 @@
         <v>45072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20817,7 +20817,7 @@
         <v>45062</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>45086</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45989</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45989</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>44979</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21192,7 +21192,7 @@
         <v>44886</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21265,7 +21265,7 @@
         <v>45995</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21343,7 +21343,7 @@
         <v>45996</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>45079</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>46003</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>46003</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>45301</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>45343</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>46008</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46008</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45204</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
         <v>44809</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22239,7 +22239,7 @@
         <v>45581</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22312,7 +22312,7 @@
         <v>45020</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22385,7 +22385,7 @@
         <v>44914</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45301</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22531,7 +22531,7 @@
         <v>45301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>46030</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22682,7 +22682,7 @@
         <v>45163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45782</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45600</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>45600</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22989,7 +22989,7 @@
         <v>44614</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23067,7 +23067,7 @@
         <v>45324</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45943</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>46036</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>46044</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45301</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46146</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>46069</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46152</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>46071</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>46080</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>46085</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23963,7 +23963,7 @@
         <v>45973</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24041,7 +24041,7 @@
         <v>45809</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24114,7 +24114,7 @@
         <v>46167</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45747</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>46189</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>45917</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46196</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>46199</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>46205</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>46205</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>46205</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>46205</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>45986</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>46218</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25015,7 +25015,7 @@
         <v>46265</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46178</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>46226</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>46226</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>46274</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>46273</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>46274</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>46276</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>46276</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>46275</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>46238</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25838,7 +25838,7 @@
         <v>46238</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46239</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>46239</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>46188</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>46286</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>46274</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>46218</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>46286</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>46244</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>46287</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>46247</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26676,7 +26676,7 @@
         <v>46290</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26749,7 +26749,7 @@
         <v>46244</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         <v>46247</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26900,7 +26900,7 @@
         <v>45924</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26973,7 +26973,7 @@
         <v>46290</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27046,7 +27046,7 @@
         <v>46248</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27124,7 +27124,7 @@
         <v>46251</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>46300</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27280,7 +27280,7 @@
         <v>46300</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45537</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         <v>45929</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27509,7 +27509,7 @@
         <v>45943</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27587,7 +27587,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27665,7 +27665,7 @@
         <v>45996</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46189</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27899,7 +27899,7 @@
         <v>46196</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44907</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46177</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46008</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46132</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45532</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45870</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44740</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>46101</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45190</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>46197</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>46303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46307</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45705</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45591</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45460</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44711</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45758</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44657</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44545</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45062</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45327</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45670</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45335</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45190</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45020</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45086</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45467</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45733</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45943</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45782</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45554</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45156</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45050</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45896</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45902</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45670</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45918</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45929</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>46152</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45187</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44914</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45943</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44803</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45943</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45943</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45947</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45320</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45713</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45880</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45877</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45877</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45965</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45965</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45965</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44557</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45758</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45021</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45152</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45462</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45390</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45981</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>46167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45809</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44886</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45027</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45986</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45989</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44488</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45337</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45020</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45747</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45995</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45996</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45079</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45324</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45551</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46003</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46003</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45145</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45614</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>46030</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>46036</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45747</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46044</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>44908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45072</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45429</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45086</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44872</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>44886</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44886</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>46080</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45769</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>44515</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45629</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45580</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46101</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45600</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45462</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44858</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44650</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45301</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45343</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44831</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>46205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>46205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46205</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>46218</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45020</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46178</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45986</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>46226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>46226</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46273</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45097</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46274</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45156</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46275</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>46274</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45673</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44822</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46276</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>46276</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45702</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>46238</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45020</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44859</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45747</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>46238</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45364</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>46239</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46188</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46239</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45062</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46287</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46218</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46286</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46286</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46274</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44858</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45258</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44914</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45758</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45301</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45301</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45163</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44672</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>46247</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46248</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45365</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45210</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45089</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45020</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45020</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45301</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46300</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45554</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45782</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46300</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45342</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45147</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46265</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45222</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45825</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45855</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45860</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45867</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45867</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45867</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45869</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45860</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45860</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45860</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45943</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>46196</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>44907</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>45894</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>46002</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46008</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46177</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46008</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46029</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>46132</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45532</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45870</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45092</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3606,7 +3606,7 @@
         <v>44740</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
         <v>46101</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         <v>45429</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>44593</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>44673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>45911</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4368,7 +4368,7 @@
         <v>45610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>45106</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         <v>46021</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>45369</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>45190</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>46197</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5122,7 +5122,7 @@
         <v>46286</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>45246</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>46303</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>46307</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45117</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>44580</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>45869</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45705</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>44852</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44545</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>45591</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>44728</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         <v>45460</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8585,7 +8585,7 @@
         <v>44711</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>45758</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8741,7 +8741,7 @@
         <v>44657</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44557</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>44545</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
         <v>45747</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9038,7 +9038,7 @@
         <v>45301</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45301</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9184,7 +9184,7 @@
         <v>45062</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>45163</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45327</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45670</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45204</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9564,7 +9564,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45335</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9720,7 +9720,7 @@
         <v>45729</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>45222</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9871,7 +9871,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>45190</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>45141</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>45020</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>45086</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10246,7 +10246,7 @@
         <v>45720</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45062</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10392,7 +10392,7 @@
         <v>45259</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>45146</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>45698</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10616,7 +10616,7 @@
         <v>45604</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10689,7 +10689,7 @@
         <v>45078</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>45467</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10840,7 +10840,7 @@
         <v>45733</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>45163</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10991,7 +10991,7 @@
         <v>44809</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>45163</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>44836</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>45943</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11293,7 +11293,7 @@
         <v>45782</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11366,7 +11366,7 @@
         <v>45554</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
         <v>45156</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11512,7 +11512,7 @@
         <v>45678</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>45896</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>45050</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>45896</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45511</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11882,7 +11882,7 @@
         <v>45902</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>45670</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>45911</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12106,7 +12106,7 @@
         <v>45614</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12262,7 +12262,7 @@
         <v>45917</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12340,7 +12340,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12418,7 +12418,7 @@
         <v>45917</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45919</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>45918</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12642,7 +12642,7 @@
         <v>46146</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45924</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>45929</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12861,7 +12861,7 @@
         <v>45930</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         <v>46152</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>45187</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13085,7 +13085,7 @@
         <v>44692</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13158,7 +13158,7 @@
         <v>44914</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13231,7 +13231,7 @@
         <v>45259</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13304,7 +13304,7 @@
         <v>45943</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>45943</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13460,7 +13460,7 @@
         <v>44803</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13533,7 +13533,7 @@
         <v>45943</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13611,7 +13611,7 @@
         <v>45943</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45945</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>45947</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45320</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>45954</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>44937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>45954</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14147,7 +14147,7 @@
         <v>45713</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14225,7 +14225,7 @@
         <v>45880</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14303,7 +14303,7 @@
         <v>45877</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14381,7 +14381,7 @@
         <v>45877</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45817</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45965</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45965</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45965</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>44557</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45758</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>46085</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>44980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45021</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45152</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45462</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>44979</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45390</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45981</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>46167</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15574,7 +15574,7 @@
         <v>45809</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>44886</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15720,7 +15720,7 @@
         <v>45027</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>45986</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>45989</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16110,7 +16110,7 @@
         <v>45989</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
         <v>45020</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16261,7 +16261,7 @@
         <v>44488</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16334,7 +16334,7 @@
         <v>45337</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>45537</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45020</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45747</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>44497</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16709,7 +16709,7 @@
         <v>45995</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>45996</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45559</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45079</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45324</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>45551</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46003</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46003</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>46008</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>46008</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>45145</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45614</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>46030</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17703,7 +17703,7 @@
         <v>46036</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17776,7 +17776,7 @@
         <v>45747</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46044</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17927,7 +17927,7 @@
         <v>45013</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18000,7 +18000,7 @@
         <v>45552</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18078,7 +18078,7 @@
         <v>44980</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>44908</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>46069</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45072</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45429</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45086</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44872</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>44886</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>44886</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>46080</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19052,7 +19052,7 @@
         <v>45769</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>44515</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19203,7 +19203,7 @@
         <v>46189</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>45629</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45917</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45580</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46196</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19583,7 +19583,7 @@
         <v>45973</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>46101</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45600</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19817,7 +19817,7 @@
         <v>45600</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45462</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>45117</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45078</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44858</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44650</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45301</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45343</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>44831</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20728,7 +20728,7 @@
         <v>45937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20801,7 +20801,7 @@
         <v>46205</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20874,7 +20874,7 @@
         <v>46205</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20947,7 +20947,7 @@
         <v>46205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>46205</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21093,7 +21093,7 @@
         <v>45226</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21166,7 +21166,7 @@
         <v>45614</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21244,7 +21244,7 @@
         <v>46218</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21317,7 +21317,7 @@
         <v>45020</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21390,7 +21390,7 @@
         <v>46178</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
         <v>45986</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>46226</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>46226</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46273</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21770,7 +21770,7 @@
         <v>45097</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>46274</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45156</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46275</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
         <v>46274</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22145,7 +22145,7 @@
         <v>45673</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22223,7 +22223,7 @@
         <v>44822</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>46276</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
         <v>46276</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22442,7 +22442,7 @@
         <v>45702</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>45222</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>46238</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45020</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22739,7 +22739,7 @@
         <v>44859</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22817,7 +22817,7 @@
         <v>45747</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22895,7 +22895,7 @@
         <v>46238</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22973,7 +22973,7 @@
         <v>45364</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23046,7 +23046,7 @@
         <v>46239</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>46188</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45146</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>46239</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>45062</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>44904</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>46287</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>46218</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46286</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>46286</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>46244</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>46274</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>44858</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24025,7 +24025,7 @@
         <v>45258</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24103,7 +24103,7 @@
         <v>44914</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45758</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>46244</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45301</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45301</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>46290</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45163</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45924</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44672</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>46247</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45072</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>46290</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>46248</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>46247</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45365</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45210</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>46251</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44942</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45089</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45020</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45020</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45301</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>46300</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45554</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25895,7 +25895,7 @@
         <v>45782</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>46300</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26046,7 +26046,7 @@
         <v>45342</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26119,7 +26119,7 @@
         <v>45147</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>45797</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>45467</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46265</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45809</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45222</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45825</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45855</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>45860</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45867</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45867</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45867</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45869</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45860</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45860</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45860</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>45537</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45929</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27463,7 +27463,7 @@
         <v>45943</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27541,7 +27541,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27619,7 +27619,7 @@
         <v>45996</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27697,7 +27697,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27775,7 +27775,7 @@
         <v>46189</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>46196</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46002</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46177</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45870</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46132</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45429</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44740</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45911</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46197</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>46286</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45117</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44580</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45869</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46307</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45369</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45190</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>45106</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45705</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45062</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45301</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45020</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45729</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45301</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45911</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45809</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45924</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45429</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45943</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45943</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45945</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45554</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45301</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45877</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45877</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45880</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45965</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45365</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45390</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46199</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45511</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45259</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45981</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45259</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44545</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>46205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>46205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46205</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45986</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45013</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45335</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45995</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45301</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45996</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46218</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45554</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>46178</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>46226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>46226</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45782</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>46003</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>46003</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45342</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>46238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>46238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46239</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>46239</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46188</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46286</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46218</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46286</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>46244</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46044</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>46247</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45021</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>46244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46247</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45809</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>46290</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46248</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>46069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>46071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>46251</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45222</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46300</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>46101</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>44858</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45855</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45860</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45867</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45867</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45867</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45869</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45860</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45860</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>46265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45343</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45937</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45670</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>44809</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45581</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44692</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45551</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45559</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45163</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44937</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45782</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>46287</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45943</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44886</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44886</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44887</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46273</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45580</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>46276</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45614</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45614</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46274</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46274</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46276</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44711</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46146</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>46275</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44872</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44672</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44942</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45670</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45089</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45020</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45020</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45462</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45163</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44980</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45027</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45020</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45678</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45673</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44858</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45072</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45062</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45086</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44886</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45117</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45747</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45337</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>44836</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44904</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44557</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44557</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45086</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44515</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45020</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45614</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45758</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>44980</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45587</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44914</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45146</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45156</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45020</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45020</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45020</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45152</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45591</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45146</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45604</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45078</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44803</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44657</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45769</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45141</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>44822</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45698</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45156</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44728</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44650</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45460</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45187</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45222</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45720</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45320</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45327</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45758</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45733</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45462</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45702</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44979</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45943</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>46189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>46196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>

--- a/Översikt BOXHOLM.xlsx
+++ b/Översikt BOXHOLM.xlsx
@@ -601,7 +601,7 @@
         <v>44875</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
         <v>45911</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>45904</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>46002</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>44887</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>46008</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>46286</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>45904</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1586,7 +1586,7 @@
         <v>45372</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         <v>45894</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>46002</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>44907</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2043,7 +2043,7 @@
         <v>45869</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
         <v>46177</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>46008</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46029</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46008</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45532</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45870</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>46132</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         <v>44494</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         <v>45996</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44693</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>45170</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>45429</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>46002</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>46101</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         <v>45092</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>44740</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4048,7 +4048,7 @@
         <v>45911</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>45246</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4267,7 +4267,7 @@
         <v>46197</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4377,7 +4377,7 @@
         <v>45610</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4482,7 +4482,7 @@
         <v>46021</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
         <v>46286</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4702,7 +4702,7 @@
         <v>45117</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44580</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>45869</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>46307</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>44673</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>45369</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45190</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>44593</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5681,7 +5681,7 @@
         <v>45106</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45705</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46296</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44873</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44507</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44886</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44841</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44673</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44711</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6559,7 +6559,7 @@
         <v>44523</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44866</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44834</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44665</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44832</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44747</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>44673</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7090,7 +7090,7 @@
         <v>44852</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7163,7 +7163,7 @@
         <v>44832</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
         <v>44832</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>44537</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>44545</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         <v>44538</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>44728</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>44575</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7689,7 +7689,7 @@
         <v>44523</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>44832</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44747</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>44803</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7991,7 +7991,7 @@
         <v>44846</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>44866</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44523</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         <v>45079</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44852</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
         <v>44545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8434,7 +8434,7 @@
         <v>45062</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8507,7 +8507,7 @@
         <v>45301</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>45747</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8658,7 +8658,7 @@
         <v>45896</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>45896</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8804,7 +8804,7 @@
         <v>45204</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8877,7 +8877,7 @@
         <v>45020</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8950,7 +8950,7 @@
         <v>45729</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>44914</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45301</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45301</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45911</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>45600</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9476,7 +9476,7 @@
         <v>45600</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9554,7 +9554,7 @@
         <v>44614</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>45809</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9705,7 +9705,7 @@
         <v>45324</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9783,7 +9783,7 @@
         <v>45918</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>45917</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>45917</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45917</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45917</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45919</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46167</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45924</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10470,7 +10470,7 @@
         <v>45929</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10543,7 +10543,7 @@
         <v>45930</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>45943</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10699,7 +10699,7 @@
         <v>45429</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10772,7 +10772,7 @@
         <v>45943</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45943</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45943</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>45945</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45554</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>45301</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>45222</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>45947</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11376,7 +11376,7 @@
         <v>45954</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45954</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45210</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>45877</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45877</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>45880</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11839,7 +11839,7 @@
         <v>46189</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>45965</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11990,7 +11990,7 @@
         <v>45965</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45965</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45467</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>45226</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12282,7 +12282,7 @@
         <v>45365</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12355,7 +12355,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12428,7 +12428,7 @@
         <v>45390</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12506,7 +12506,7 @@
         <v>45747</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>46196</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12662,7 +12662,7 @@
         <v>46199</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>45511</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12808,7 +12808,7 @@
         <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12886,7 +12886,7 @@
         <v>45259</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12959,7 +12959,7 @@
         <v>45981</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13032,7 +13032,7 @@
         <v>45259</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45097</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44545</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44859</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>46205</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>46205</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>46205</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45758</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>46205</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>45986</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13782,7 +13782,7 @@
         <v>45986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45013</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45989</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45258</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45335</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45995</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14323,7 +14323,7 @@
         <v>45301</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14396,7 +14396,7 @@
         <v>45996</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45986</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>46218</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45554</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>46178</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>46226</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>46226</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45782</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>45147</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>46003</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>46003</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>46008</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>46008</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45342</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15443,7 +15443,7 @@
         <v>46238</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>46238</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15599,7 +15599,7 @@
         <v>46239</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15677,7 +15677,7 @@
         <v>46239</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>46188</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15833,7 +15833,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>46286</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>46036</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>46274</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>46218</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>46286</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>46244</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16359,7 +16359,7 @@
         <v>46044</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16432,7 +16432,7 @@
         <v>45797</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>45467</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16578,7 +16578,7 @@
         <v>46247</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>45021</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>46290</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>46244</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>46247</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45924</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45809</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>46290</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>46248</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>46069</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>46071</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>46251</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46080</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45222</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>45973</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46300</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>46101</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>45825</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18020,7 +18020,7 @@
         <v>44858</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         <v>45855</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         <v>45860</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18244,7 +18244,7 @@
         <v>45867</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>45867</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45867</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>45869</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45860</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45860</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>45860</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>46265</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>44908</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45343</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45937</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45670</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>44809</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45581</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44692</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45551</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19452,7 +19452,7 @@
         <v>45559</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45163</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>44937</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45782</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>46287</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45943</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19905,7 +19905,7 @@
         <v>45222</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>44886</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44886</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20124,7 +20124,7 @@
         <v>44887</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45552</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46273</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20358,7 +20358,7 @@
         <v>45301</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>45580</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>46276</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20577,7 +20577,7 @@
         <v>45614</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20655,7 +20655,7 @@
         <v>45614</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>46274</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>46274</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>46276</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44711</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46146</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>46275</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44872</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>46152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         <v>44672</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21405,7 +21405,7 @@
         <v>44942</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21478,7 +21478,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
         <v>45670</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21629,7 +21629,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>46085</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21775,7 +21775,7 @@
         <v>45089</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21848,7 +21848,7 @@
         <v>45020</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45020</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44497</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>45145</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45462</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22218,7 +22218,7 @@
         <v>45163</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22296,7 +22296,7 @@
         <v>45163</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>44980</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22447,7 +22447,7 @@
         <v>45072</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22520,7 +22520,7 @@
         <v>45027</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22598,7 +22598,7 @@
         <v>45020</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45678</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22749,7 +22749,7 @@
         <v>45673</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22827,7 +22827,7 @@
         <v>44858</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45072</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45062</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23051,7 +23051,7 @@
         <v>45086</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23124,7 +23124,7 @@
         <v>44886</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23197,7 +23197,7 @@
         <v>45117</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>45747</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23353,7 +23353,7 @@
         <v>44887</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45337</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>44836</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>44904</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45050</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45078</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23801,7 +23801,7 @@
         <v>44557</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>44557</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23947,7 +23947,7 @@
         <v>45086</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24020,7 +24020,7 @@
         <v>44515</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24093,7 +24093,7 @@
         <v>45020</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45614</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45758</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>44980</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45587</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -24473,7 +24473,7 @@
         <v>44914</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>45146</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45537</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>45156</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24775,7 +24775,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24853,7 +24853,7 @@
         <v>45020</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24926,7 +24926,7 @@
         <v>45020</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>45020</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25072,7 +25072,7 @@
         <v>45152</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25145,7 +25145,7 @@
         <v>45591</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25218,7 +25218,7 @@
         <v>45146</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25291,7 +25291,7 @@
         <v>45604</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25364,7 +25364,7 @@
         <v>45078</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45190</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -25515,7 +25515,7 @@
         <v>44803</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25588,7 +25588,7 @@
         <v>44657</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25661,7 +25661,7 @@
         <v>45769</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>45141</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>44822</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25885,7 +25885,7 @@
         <v>45698</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>45156</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>44728</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>44650</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26187,7 +26187,7 @@
         <v>45460</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>45187</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45062</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45222</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45720</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45320</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26635,7 +26635,7 @@
         <v>45327</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26713,7 +26713,7 @@
         <v>45758</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26791,7 +26791,7 @@
         <v>45364</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26864,7 +26864,7 @@
         <v>44831</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>45733</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45462</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45702</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>44979</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45537</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27317,7 +27317,7 @@
         <v>45929</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45943</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -27468,7 +27468,7 @@
         <v>45996</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -27546,7 +27546,7 @@
         <v>45996</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>46189</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         <v>46189</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>46196</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
